--- a/internal_doc/02.架构框架/SequoiaDB述语表.xlsx
+++ b/internal_doc/02.架构框架/SequoiaDB述语表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
   <si>
     <t>述语</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,6 +92,170 @@
   </si>
   <si>
     <t xml:space="preserve">Data management services </t>
+  </si>
+  <si>
+    <t xml:space="preserve">include </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mdocml </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mig </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">msg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mth </t>
+  </si>
+  <si>
+    <t xml:space="preserve">net </t>
+  </si>
+  <si>
+    <t xml:space="preserve">opt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">oss </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data protection services </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mdocml -- open source man page generator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Messages </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methods </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimizer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating system services </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pcre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">qgm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rest </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rtn </t>
+  </si>
+  <si>
+    <t xml:space="preserve">snappy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">spd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation management agent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perl compatible regular expression </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problem determination </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Query graph management </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REST </t>
+  </si>
+  <si>
+    <t xml:space="preserve">runtime </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary process daemon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">spt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools </t>
+  </si>
+  <si>
+    <t xml:space="preserve">util </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pmd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ixm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operation management service </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Script </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process Model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster Manager </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index Manager </t>
+  </si>
+  <si>
+    <t>edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engine Dispatchable Unit </t>
+  </si>
+  <si>
+    <t>repl</t>
+  </si>
+  <si>
+    <t>Replication</t>
+  </si>
+  <si>
+    <t>shard</t>
+  </si>
+  <si>
+    <t>Shard</t>
+  </si>
+  <si>
+    <t>Fenced Mode Process</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔离模式进程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -101,69 +265,12 @@
       <rPr>
         <b/>
         <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">include </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mdocml </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mig </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mon </t>
-  </si>
-  <si>
-    <t xml:space="preserve">msg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mth </t>
-  </si>
-  <si>
-    <t xml:space="preserve">net </t>
-  </si>
-  <si>
-    <t xml:space="preserve">opt </t>
-  </si>
-  <si>
-    <t xml:space="preserve">oss </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data protection services </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mdocml -- open source man page generator </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migration </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Messages </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Methods </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimizer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating system services </t>
   </si>
   <si>
     <r>
@@ -173,54 +280,12 @@
       <rPr>
         <b/>
         <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">pcre </t>
-  </si>
-  <si>
-    <t xml:space="preserve">pd </t>
-  </si>
-  <si>
-    <t xml:space="preserve">qgm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rest </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rtn </t>
-  </si>
-  <si>
-    <t xml:space="preserve">snappy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">spd </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operation management agent </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perl compatible regular expression </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problem determination </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Query graph management </t>
-  </si>
-  <si>
-    <t xml:space="preserve">REST </t>
-  </si>
-  <si>
-    <t xml:space="preserve">runtime </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secondary process daemon </t>
   </si>
   <si>
     <r>
@@ -230,7 +295,7 @@
       <rPr>
         <b/>
         <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
@@ -238,68 +303,75 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">spt </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tools </t>
-  </si>
-  <si>
-    <t xml:space="preserve">util </t>
-  </si>
-  <si>
-    <t xml:space="preserve">pmd </t>
-  </si>
-  <si>
-    <t xml:space="preserve">cm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ixm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operation management service </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Script </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tools </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Process Model </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster Manager </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Index Manager </t>
-  </si>
-  <si>
-    <t>edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engine Dispatchable Unit </t>
-  </si>
-  <si>
-    <t>repl</t>
-  </si>
-  <si>
-    <t>Replication</t>
-  </si>
-  <si>
-    <t>shard</t>
-  </si>
-  <si>
-    <t>Shard</t>
+    <t>fmp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴权</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备份恢复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据管理服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据保护服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题诊断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程模型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询图型管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Foreign Access Protocol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外部接入协议</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,13 +385,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="18"/>
@@ -339,6 +404,32 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000099"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000099"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -424,8 +515,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -435,22 +535,37 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -779,792 +894,828 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="C2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="12"/>
     </row>
     <row r="3" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="C3" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="14"/>
     </row>
     <row r="4" spans="1:4" ht="24" thickBot="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="1:4" ht="24" thickBot="1">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="24" thickBot="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4" ht="24" thickBot="1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
     </row>
     <row r="8" spans="1:4" ht="24" thickBot="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:4" ht="24" thickBot="1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
     </row>
     <row r="10" spans="1:4" ht="24" thickBot="1">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:4" ht="24" thickBot="1">
+      <c r="A11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="1:4" ht="24" thickBot="1">
+      <c r="A12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="14"/>
+    </row>
+    <row r="13" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
+      <c r="A13" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="1:4" ht="24" thickBot="1">
+      <c r="A14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="1:4" ht="24" thickBot="1">
+      <c r="A15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:4" ht="47.25" thickBot="1">
+      <c r="A16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="1:4" ht="24" thickBot="1">
+      <c r="A17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:4" ht="24" thickBot="1">
+      <c r="A18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="1:4" ht="24" thickBot="1">
+      <c r="A19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4" ht="24" thickBot="1">
+      <c r="A20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" spans="1:4" ht="24" thickBot="1">
+      <c r="A21" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="1:4" ht="24" thickBot="1">
+      <c r="A22" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
+      <c r="A23" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:4" ht="24" thickBot="1">
+      <c r="A24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:4" ht="24" thickBot="1">
+      <c r="A25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="14"/>
+    </row>
+    <row r="26" spans="1:4" ht="24" thickBot="1">
+      <c r="A26" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+    </row>
+    <row r="27" spans="1:4" ht="24" thickBot="1">
+      <c r="A27" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="12"/>
+    </row>
+    <row r="28" spans="1:4" ht="24" thickBot="1">
+      <c r="A28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" spans="1:4" ht="24" thickBot="1">
+      <c r="A29" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="14"/>
+    </row>
+    <row r="30" spans="1:4" ht="24" thickBot="1">
+      <c r="A30" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
+      <c r="A31" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="14"/>
+    </row>
+    <row r="32" spans="1:4" ht="24" thickBot="1">
+      <c r="A32" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+    </row>
+    <row r="33" spans="1:4" ht="24" thickBot="1">
+      <c r="A33" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+    </row>
+    <row r="34" spans="1:4" ht="24" thickBot="1">
+      <c r="A34" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" ht="24" thickBot="1">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" ht="24" thickBot="1">
-      <c r="A12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
-      <c r="A13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" ht="24" thickBot="1">
-      <c r="A14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="1:4" ht="24" thickBot="1">
-      <c r="A15" s="2" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+    </row>
+    <row r="35" spans="1:4" ht="24" thickBot="1">
+      <c r="A35" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" ht="47.25" thickBot="1">
-      <c r="A16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" ht="24" thickBot="1">
-      <c r="A17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="1:4" ht="24" thickBot="1">
-      <c r="A18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="1:4" ht="24" thickBot="1">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" ht="24" thickBot="1">
-      <c r="A20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:4" ht="24" thickBot="1">
-      <c r="A21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="1:4" ht="24" thickBot="1">
-      <c r="A22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
-      <c r="A23" s="8" t="s">
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+    </row>
+    <row r="36" spans="1:4" ht="24" thickBot="1">
+      <c r="A36" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B36" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="1:4" ht="24" thickBot="1">
-      <c r="A24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:4" ht="24" thickBot="1">
-      <c r="A25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" spans="1:4" ht="24" thickBot="1">
-      <c r="A26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="1:4" ht="24" thickBot="1">
-      <c r="A27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="1:4" ht="24" thickBot="1">
-      <c r="A28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="1:4" ht="24" thickBot="1">
-      <c r="A29" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" spans="1:4" ht="24" thickBot="1">
-      <c r="A30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
-      <c r="A31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" spans="1:4" ht="24" thickBot="1">
-      <c r="A32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" spans="1:4" ht="24" thickBot="1">
-      <c r="A33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-    </row>
-    <row r="34" spans="1:4" ht="24" thickBot="1">
-      <c r="A34" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-    </row>
-    <row r="35" spans="1:4" ht="24" thickBot="1">
-      <c r="A35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="1:4" ht="24" thickBot="1">
-      <c r="A36" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
     </row>
     <row r="37" spans="1:4" ht="24" thickBot="1">
-      <c r="A37" s="3"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
+      <c r="A37" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="14"/>
     </row>
     <row r="38" spans="1:4" ht="24" thickBot="1">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="A38" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="12"/>
     </row>
     <row r="39" spans="1:4" ht="24" thickBot="1">
-      <c r="A39" s="3"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
     </row>
     <row r="40" spans="1:4" ht="24" thickBot="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
     </row>
     <row r="41" spans="1:4" ht="24" thickBot="1">
-      <c r="A41" s="3"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
     </row>
     <row r="42" spans="1:4" ht="24" thickBot="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
     </row>
     <row r="43" spans="1:4" ht="24" thickBot="1">
-      <c r="A43" s="3"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
     </row>
     <row r="44" spans="1:4" ht="24" thickBot="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
     </row>
     <row r="45" spans="1:4" ht="24" thickBot="1">
-      <c r="A45" s="3"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
     </row>
     <row r="46" spans="1:4" ht="24" thickBot="1">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
     </row>
     <row r="47" spans="1:4" ht="24" thickBot="1">
-      <c r="A47" s="3"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
     </row>
     <row r="48" spans="1:4" ht="24" thickBot="1">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
     </row>
     <row r="49" spans="1:4" ht="24" thickBot="1">
-      <c r="A49" s="3"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
     </row>
     <row r="50" spans="1:4" ht="24" thickBot="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
     </row>
     <row r="51" spans="1:4" ht="24" thickBot="1">
-      <c r="A51" s="3"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
+      <c r="A51" s="10"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
     </row>
     <row r="52" spans="1:4" ht="24" thickBot="1">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
     </row>
     <row r="53" spans="1:4" ht="24" thickBot="1">
-      <c r="A53" s="3"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
     </row>
     <row r="54" spans="1:4" ht="24" thickBot="1">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
     </row>
     <row r="55" spans="1:4" ht="24" thickBot="1">
-      <c r="A55" s="3"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
     </row>
     <row r="56" spans="1:4" ht="24" thickBot="1">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
+      <c r="A56" s="8"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
     </row>
     <row r="57" spans="1:4" ht="24" thickBot="1">
-      <c r="A57" s="3"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
     </row>
     <row r="58" spans="1:4" ht="24" thickBot="1">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
     </row>
     <row r="59" spans="1:4" ht="24" thickBot="1">
-      <c r="A59" s="3"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
     </row>
     <row r="60" spans="1:4" ht="24" thickBot="1">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
     </row>
     <row r="61" spans="1:4" ht="24" thickBot="1">
-      <c r="A61" s="3"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="A61" s="10"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
     </row>
     <row r="62" spans="1:4" ht="24" thickBot="1">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="A62" s="8"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
     </row>
     <row r="63" spans="1:4" ht="24" thickBot="1">
-      <c r="A63" s="3"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="A63" s="10"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
     </row>
     <row r="64" spans="1:4" ht="24" thickBot="1">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:4" ht="24" thickBot="1">
-      <c r="A65" s="3"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
     </row>
     <row r="66" spans="1:4" ht="24" thickBot="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
+      <c r="A66" s="8"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:4" ht="24" thickBot="1">
-      <c r="A67" s="3"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
+      <c r="A67" s="10"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
     </row>
     <row r="68" spans="1:4" ht="24" thickBot="1">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
+      <c r="A68" s="8"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
     </row>
     <row r="69" spans="1:4" ht="24" thickBot="1">
-      <c r="A69" s="3"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
     </row>
     <row r="70" spans="1:4" ht="24" thickBot="1">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
+      <c r="A70" s="8"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
     </row>
     <row r="71" spans="1:4" ht="24" thickBot="1">
-      <c r="A71" s="3"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
     </row>
     <row r="72" spans="1:4" ht="24" thickBot="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="A72" s="8"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
     </row>
     <row r="73" spans="1:4" ht="24" thickBot="1">
-      <c r="A73" s="3"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
+      <c r="A73" s="10"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
     </row>
     <row r="74" spans="1:4" ht="24" thickBot="1">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
+      <c r="A74" s="8"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
     </row>
     <row r="75" spans="1:4" ht="24" thickBot="1">
-      <c r="A75" s="3"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
+      <c r="A75" s="10"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
     </row>
     <row r="76" spans="1:4" ht="24" thickBot="1">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
+      <c r="A76" s="8"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
     </row>
     <row r="77" spans="1:4" ht="24" thickBot="1">
-      <c r="A77" s="3"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
+      <c r="A77" s="10"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
     </row>
     <row r="78" spans="1:4" ht="24" thickBot="1">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
+      <c r="A78" s="8"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
     </row>
     <row r="79" spans="1:4" ht="24" thickBot="1">
-      <c r="A79" s="3"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
+      <c r="A79" s="10"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
     </row>
     <row r="80" spans="1:4" ht="24" thickBot="1">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
     </row>
     <row r="81" spans="1:4" ht="24" thickBot="1">
-      <c r="A81" s="3"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
+      <c r="A81" s="10"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
     </row>
     <row r="82" spans="1:4" ht="24" thickBot="1">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
+      <c r="A82" s="8"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
     </row>
     <row r="83" spans="1:4" ht="24" thickBot="1">
-      <c r="A83" s="3"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
+      <c r="A83" s="10"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
     </row>
     <row r="84" spans="1:4" ht="24" thickBot="1">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
+      <c r="A84" s="8"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
     </row>
     <row r="85" spans="1:4" ht="24" thickBot="1">
-      <c r="A85" s="3"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
+      <c r="A85" s="10"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
     </row>
     <row r="86" spans="1:4" ht="24" thickBot="1">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
+      <c r="A86" s="8"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="12"/>
     </row>
     <row r="87" spans="1:4" ht="24" thickBot="1">
-      <c r="A87" s="3"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
+      <c r="A87" s="10"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
     </row>
     <row r="88" spans="1:4" ht="24" thickBot="1">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
+      <c r="A88" s="8"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
     </row>
     <row r="89" spans="1:4" ht="24" thickBot="1">
-      <c r="A89" s="3"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
+      <c r="A89" s="10"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
     </row>
     <row r="90" spans="1:4" ht="24" thickBot="1">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+      <c r="A90" s="8"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
     </row>
     <row r="91" spans="1:4" ht="24" thickBot="1">
-      <c r="A91" s="3"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
+      <c r="A91" s="10"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
     </row>
     <row r="92" spans="1:4" ht="24" thickBot="1">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
+      <c r="A92" s="8"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
     </row>
     <row r="93" spans="1:4" ht="24" thickBot="1">
-      <c r="A93" s="3"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
+      <c r="A93" s="10"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
     </row>
     <row r="94" spans="1:4" ht="24" thickBot="1">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
+      <c r="A94" s="8"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
     </row>
     <row r="95" spans="1:4" ht="24" thickBot="1">
-      <c r="A95" s="3"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
+      <c r="A95" s="10"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="14"/>
     </row>
     <row r="96" spans="1:4" ht="24" thickBot="1">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
+      <c r="A96" s="8"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
     </row>
     <row r="97" spans="1:4" ht="24" thickBot="1">
-      <c r="A97" s="3"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
+      <c r="A97" s="10"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
     </row>
     <row r="98" spans="1:4" ht="24" thickBot="1">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
+      <c r="A98" s="8"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
     </row>
     <row r="99" spans="1:4" ht="24" thickBot="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
+      <c r="A99" s="10"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="14"/>
     </row>
     <row r="100" spans="1:4" ht="24" thickBot="1">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
+      <c r="A100" s="8"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
     </row>
     <row r="101" spans="1:4" ht="24" thickBot="1">
-      <c r="A101" s="3"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
+      <c r="A101" s="10"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
     </row>
     <row r="102" spans="1:4" ht="24" thickBot="1">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="A102" s="8"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
     </row>
     <row r="103" spans="1:4" ht="24" thickBot="1">
-      <c r="A103" s="3"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
+      <c r="A103" s="10"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
+      <c r="D103" s="14"/>
     </row>
     <row r="104" spans="1:4" ht="24" thickBot="1">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
+      <c r="A104" s="8"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
     </row>
     <row r="105" spans="1:4" ht="24" thickBot="1">
-      <c r="A105" s="3"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
+      <c r="A105" s="10"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="14"/>
     </row>
     <row r="106" spans="1:4" ht="24" thickBot="1">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
+      <c r="A106" s="8"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
     </row>
     <row r="107" spans="1:4" ht="24" thickBot="1">
-      <c r="A107" s="3"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
+      <c r="A107" s="10"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
     </row>
     <row r="108" spans="1:4" ht="24" thickBot="1">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
+      <c r="A108" s="8"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
     </row>
     <row r="109" spans="1:4" ht="24" thickBot="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
+      <c r="A109" s="10"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14"/>
     </row>
   </sheetData>
   <sortState ref="A2:D36">
@@ -1606,30 +1757,30 @@
     </row>
     <row r="2" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4" ht="24.75" thickTop="1" thickBot="1">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="24" thickBot="1">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
